--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EAB4F9-2003-4F91-B0FC-A1B9CA2D11F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D55302B-6FDB-477C-8815-920C4D87525A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
   <si>
     <t>idstring</t>
   </si>
@@ -200,6 +200,33 @@
   </si>
   <si>
     <t>надеть</t>
+  </si>
+  <si>
+    <t>Health_Header</t>
+  </si>
+  <si>
+    <t>Health_Cost</t>
+  </si>
+  <si>
+    <t>Health_Description</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Cost: One characters point</t>
+  </si>
+  <si>
+    <t>Adds 10 to the character's maximum health. It also restores the current health to its maximum.</t>
+  </si>
+  <si>
+    <t>Прибавляет 10 к максимальному здоровью персонажа. А также восстанавливает текущее здоровье до максимума.</t>
+  </si>
+  <si>
+    <t>Стоимость: 1 очко параметров</t>
+  </si>
+  <si>
+    <t>Здоровье</t>
   </si>
 </sst>
 </file>
@@ -517,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18.5703125" customWidth="1"/>
@@ -744,6 +771,39 @@
       </c>
       <c r="D20" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D55302B-6FDB-477C-8815-920C4D87525A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DF9023-9A6A-4E1A-A743-098573B346E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="128">
   <si>
     <t>idstring</t>
   </si>
@@ -214,19 +214,202 @@
     <t>Health</t>
   </si>
   <si>
-    <t>Cost: One characters point</t>
-  </si>
-  <si>
     <t>Adds 10 to the character's maximum health. It also restores the current health to its maximum.</t>
   </si>
   <si>
     <t>Прибавляет 10 к максимальному здоровью персонажа. А также восстанавливает текущее здоровье до максимума.</t>
   </si>
   <si>
-    <t>Стоимость: 1 очко параметров</t>
-  </si>
-  <si>
     <t>Здоровье</t>
+  </si>
+  <si>
+    <t>DoubleJump_Header</t>
+  </si>
+  <si>
+    <t>DoubleJump_Cost</t>
+  </si>
+  <si>
+    <t>DoubleJump_Description</t>
+  </si>
+  <si>
+    <t>Extra jump</t>
+  </si>
+  <si>
+    <t>Cost: 10 gold coins</t>
+  </si>
+  <si>
+    <t>Adds an extra jump that can be performed in the air.</t>
+  </si>
+  <si>
+    <t>Дополнительный прыжок</t>
+  </si>
+  <si>
+    <t>Стоимость: 10 золотых монет</t>
+  </si>
+  <si>
+    <t>Добавляет дополнительный прыжок, который можно выполнить в воздухе.</t>
+  </si>
+  <si>
+    <t>Attack_Header</t>
+  </si>
+  <si>
+    <t>Attack_Cost</t>
+  </si>
+  <si>
+    <t>Attack_Description</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Adds +2 to the hero's attack. The attack increases all damage dealt.</t>
+  </si>
+  <si>
+    <t>Добавляет +2 к атаке героя. Атака увеличивает весь наносимый урон.</t>
+  </si>
+  <si>
+    <t>Атака</t>
+  </si>
+  <si>
+    <t>Defense_Header</t>
+  </si>
+  <si>
+    <t>Defense_Cost</t>
+  </si>
+  <si>
+    <t>Defense_Description</t>
+  </si>
+  <si>
+    <t>Defense</t>
+  </si>
+  <si>
+    <t>Adds +2 to the hero's defense. Defense reduces all damage received.</t>
+  </si>
+  <si>
+    <t>Защита</t>
+  </si>
+  <si>
+    <t>Speed_Header</t>
+  </si>
+  <si>
+    <t>Speed_Cost</t>
+  </si>
+  <si>
+    <t>Speed_Description</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>Скорость</t>
+  </si>
+  <si>
+    <t>Increases the character's movement speed.</t>
+  </si>
+  <si>
+    <t>Увеличивает скорость передвижения персонажа.</t>
+  </si>
+  <si>
+    <t>Добавляет +2 к защите героя. Защита снижает весь получаемый урон.</t>
+  </si>
+  <si>
+    <t>Attribute Points</t>
+  </si>
+  <si>
+    <t>AttributePoints_Header</t>
+  </si>
+  <si>
+    <t>AttributePoints_Cost</t>
+  </si>
+  <si>
+    <t>AttributePoints_Description</t>
+  </si>
+  <si>
+    <t>Очки характеристик</t>
+  </si>
+  <si>
+    <t>The player receives +2 attribute points after leveling up.</t>
+  </si>
+  <si>
+    <t>Игрок получает +2 очка характеристик после повышения уровня.</t>
+  </si>
+  <si>
+    <t>HUD_Health</t>
+  </si>
+  <si>
+    <t>HUD_Attack</t>
+  </si>
+  <si>
+    <t>HUD_Defense</t>
+  </si>
+  <si>
+    <t>HUD_Speed</t>
+  </si>
+  <si>
+    <t>HUD_Level</t>
+  </si>
+  <si>
+    <t>HUD_StatPoints</t>
+  </si>
+  <si>
+    <t>HUD_Bought</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Макс</t>
+  </si>
+  <si>
+    <t>Cost: Two Attribute Points</t>
+  </si>
+  <si>
+    <t>Cost: One Attribute Point</t>
+  </si>
+  <si>
+    <t>Стоимость: 1 очко характеристик</t>
+  </si>
+  <si>
+    <t>Стоимость: 2 очка характеристик</t>
+  </si>
+  <si>
+    <t>Очки характеристик:</t>
+  </si>
+  <si>
+    <t>Level:</t>
+  </si>
+  <si>
+    <t>Уровень:</t>
+  </si>
+  <si>
+    <t>Attribute Points:</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Sword_Header</t>
+  </si>
+  <si>
+    <t>Sword_Cost</t>
+  </si>
+  <si>
+    <t>Sword_Description</t>
+  </si>
+  <si>
+    <t>Cost: 5 silver coins</t>
+  </si>
+  <si>
+    <t>Simple Sword. You can use it in close combat or throw it.</t>
+  </si>
+  <si>
+    <t>Обычный меч. Им можно бить в ближнем бою или метать.</t>
+  </si>
+  <si>
+    <t>Стоимость: 5 серебряных монет</t>
+  </si>
+  <si>
+    <t>Меч</t>
   </si>
 </sst>
 </file>
@@ -544,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18.5703125" customWidth="1"/>
@@ -781,7 +964,7 @@
         <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -789,10 +972,10 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -800,10 +983,279 @@
         <v>60</v>
       </c>
       <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
         <v>63</v>
       </c>
-      <c r="D23" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>104</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" t="s">
+        <v>124</v>
+      </c>
+      <c r="D48" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DF9023-9A6A-4E1A-A743-098573B346E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C936C31-F880-4796-9DB7-7A76D6DD2D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="187">
   <si>
     <t>idstring</t>
   </si>
@@ -244,9 +244,6 @@
     <t>Дополнительный прыжок</t>
   </si>
   <si>
-    <t>Стоимость: 10 золотых монет</t>
-  </si>
-  <si>
     <t>Добавляет дополнительный прыжок, который можно выполнить в воздухе.</t>
   </si>
   <si>
@@ -400,16 +397,196 @@
     <t>Cost: 5 silver coins</t>
   </si>
   <si>
-    <t>Simple Sword. You can use it in close combat or throw it.</t>
-  </si>
-  <si>
-    <t>Обычный меч. Им можно бить в ближнем бою или метать.</t>
-  </si>
-  <si>
-    <t>Стоимость: 5 серебряных монет</t>
-  </si>
-  <si>
     <t>Меч</t>
+  </si>
+  <si>
+    <t>GoldCoin_Header</t>
+  </si>
+  <si>
+    <t>GoldCoin_Cost</t>
+  </si>
+  <si>
+    <t>GoldCoin_Description</t>
+  </si>
+  <si>
+    <t>SilverCoin_Header</t>
+  </si>
+  <si>
+    <t>SilverCoin_Cost</t>
+  </si>
+  <si>
+    <t>SilverCoin_Description</t>
+  </si>
+  <si>
+    <t>Gold Coin</t>
+  </si>
+  <si>
+    <t>A silver coin. It's worth a silver coin — shocking, isn't it?</t>
+  </si>
+  <si>
+    <t>Face value: 1 silver</t>
+  </si>
+  <si>
+    <t>Silver Coin</t>
+  </si>
+  <si>
+    <t>Серебряная монета. Она стоит серебряную монету — поразительно, правда?</t>
+  </si>
+  <si>
+    <t>Номинал: 1 серебряная</t>
+  </si>
+  <si>
+    <t>Face value: 10 silver</t>
+  </si>
+  <si>
+    <t>Номинал: 10 серебрянных</t>
+  </si>
+  <si>
+    <t>Серебряная монета</t>
+  </si>
+  <si>
+    <t>Золотая монета</t>
+  </si>
+  <si>
+    <t>GreenPotion_Cost</t>
+  </si>
+  <si>
+    <t>GreenPotion_Description</t>
+  </si>
+  <si>
+    <t>RedPotion_Cost</t>
+  </si>
+  <si>
+    <t>RedPotion_Description</t>
+  </si>
+  <si>
+    <t>BluePotion_Cost</t>
+  </si>
+  <si>
+    <t>BluePotion_Description</t>
+  </si>
+  <si>
+    <t>GoldKey_Cost</t>
+  </si>
+  <si>
+    <t>GoldKey_Description</t>
+  </si>
+  <si>
+    <t>GoldKey_Header</t>
+  </si>
+  <si>
+    <t>BluePotion_Header</t>
+  </si>
+  <si>
+    <t>RedPotion_Header</t>
+  </si>
+  <si>
+    <t>GreenPotion_Header</t>
+  </si>
+  <si>
+    <t>Purse_Header</t>
+  </si>
+  <si>
+    <t>Purse_Cost</t>
+  </si>
+  <si>
+    <t>Purse_Description</t>
+  </si>
+  <si>
+    <t>Sturdy canvas pouch.</t>
+  </si>
+  <si>
+    <t>Pouch</t>
+  </si>
+  <si>
+    <t>Cost: 15 silver coins</t>
+  </si>
+  <si>
+    <t>Cost: 8 silver coins</t>
+  </si>
+  <si>
+    <t>Gold Key</t>
+  </si>
+  <si>
+    <t>Blue Potion</t>
+  </si>
+  <si>
+    <t>Red Potion</t>
+  </si>
+  <si>
+    <t>Green Potion</t>
+  </si>
+  <si>
+    <t>Large Health Potion, restores 15 HP.</t>
+  </si>
+  <si>
+    <t>Small Health Potion, restores 5 HP.</t>
+  </si>
+  <si>
+    <t>Малое зелье здоровья, восстанавливает 5 HP.</t>
+  </si>
+  <si>
+    <t>Большое зелье здоровья, восстанавливает 15 HP.</t>
+  </si>
+  <si>
+    <t>Голубое зелье</t>
+  </si>
+  <si>
+    <t>Стоимость: 8 серебрянных</t>
+  </si>
+  <si>
+    <t>Стоимость: 15 серебрянных</t>
+  </si>
+  <si>
+    <t>Стоимость: 5 серебряных</t>
+  </si>
+  <si>
+    <t>Стоимость: 10 золотых</t>
+  </si>
+  <si>
+    <t>This key must open something. Definitely.</t>
+  </si>
+  <si>
+    <t>Золотой ключ</t>
+  </si>
+  <si>
+    <t>Красное зелье</t>
+  </si>
+  <si>
+    <t>Зеленое зелье</t>
+  </si>
+  <si>
+    <t>Кошель</t>
+  </si>
+  <si>
+    <t>Прочный холщовый мешочек.</t>
+  </si>
+  <si>
+    <t>Этот ключ должен что-то открывать. Определенно.</t>
+  </si>
+  <si>
+    <t>Это зелье должно ускорять передвижение. Наверное.</t>
+  </si>
+  <si>
+    <t>Монета из настоящего золота. Если верить надписи.</t>
+  </si>
+  <si>
+    <t>The coin is made of real gold. If you believe that.</t>
+  </si>
+  <si>
+    <t>This potion is supposed to increase movement speed. I guess.</t>
+  </si>
+  <si>
+    <t>Стоимость: 16 серебрянных</t>
+  </si>
+  <si>
+    <t>Cost: 16 silver coins</t>
+  </si>
+  <si>
+    <t>A regular sword. Can be used in melee or thrown. Deals 4 base damage in melee, or 3 when thrown.</t>
+  </si>
+  <si>
+    <t>Обычный меч. Можно использовать в ближнем бою или метать. Наносит 4 базовых урона в ближнем бою или 3 при метании.</t>
   </si>
 </sst>
 </file>
@@ -727,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="18.5703125" customWidth="1"/>
@@ -972,10 +1149,10 @@
         <v>59</v>
       </c>
       <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" t="s">
         <v>112</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1008,7 +1185,7 @@
         <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1019,138 +1196,138 @@
         <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
         <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" t="s">
         <v>78</v>
-      </c>
-      <c r="D29" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" t="s">
         <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
         <v>90</v>
-      </c>
-      <c r="D33" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" t="s">
         <v>92</v>
-      </c>
-      <c r="D35" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" t="s">
         <v>100</v>
-      </c>
-      <c r="D38" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
         <v>61</v>
@@ -1161,101 +1338,332 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C42" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" t="s">
         <v>90</v>
-      </c>
-      <c r="D42" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" t="s">
         <v>116</v>
-      </c>
-      <c r="D43" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" t="s">
         <v>108</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>109</v>
-      </c>
-      <c r="D45" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" t="s">
+        <v>185</v>
+      </c>
+      <c r="D48" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" t="s">
+        <v>181</v>
+      </c>
+      <c r="D51" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" t="s">
+        <v>133</v>
+      </c>
+      <c r="D52" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C54" t="s">
+        <v>131</v>
+      </c>
+      <c r="D54" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59" t="s">
+        <v>158</v>
+      </c>
+      <c r="D59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D60" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" t="s">
+        <v>161</v>
+      </c>
+      <c r="D61" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" t="s">
+        <v>163</v>
+      </c>
+      <c r="D63" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>151</v>
+      </c>
+      <c r="C64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" t="s">
+        <v>157</v>
+      </c>
+      <c r="D65" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" t="s">
+        <v>182</v>
+      </c>
+      <c r="D66" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>152</v>
+      </c>
+      <c r="C67" t="s">
+        <v>156</v>
+      </c>
+      <c r="D67" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" t="s">
         <v>122</v>
       </c>
-      <c r="C48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" t="s">
-        <v>125</v>
+      <c r="D68" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D69" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C936C31-F880-4796-9DB7-7A76D6DD2D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0028531E-596C-4DE7-91F1-644BD4A15F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LocalizationUI" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="196">
   <si>
     <t>idstring</t>
   </si>
@@ -587,6 +587,33 @@
   </si>
   <si>
     <t>Обычный меч. Можно использовать в ближнем бою или метать. Наносит 4 базовых урона в ближнем бою или 3 при метании.</t>
+  </si>
+  <si>
+    <t>SharkyNPC_1</t>
+  </si>
+  <si>
+    <t>Hello!</t>
+  </si>
+  <si>
+    <t>I am good Sharky.</t>
+  </si>
+  <si>
+    <t>My name is Bob.</t>
+  </si>
+  <si>
+    <t>Привет!</t>
+  </si>
+  <si>
+    <t>Я хорошая акула.</t>
+  </si>
+  <si>
+    <t>Мое имя Боб.</t>
+  </si>
+  <si>
+    <t>SharkyNPC_3</t>
+  </si>
+  <si>
+    <t>SharkyNPC_2</t>
   </si>
 </sst>
 </file>
@@ -1674,9 +1701,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568798C2-848C-4EB1-ADFF-725305B9894F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0028531E-596C-4DE7-91F1-644BD4A15F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819CFD6F-0FFB-4F50-9A1F-831ADAB87623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="2205" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LocalizationUI" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="211">
   <si>
     <t>idstring</t>
   </si>
@@ -235,9 +238,6 @@
     <t>Extra jump</t>
   </si>
   <si>
-    <t>Cost: 10 gold coins</t>
-  </si>
-  <si>
     <t>Adds an extra jump that can be performed in the air.</t>
   </si>
   <si>
@@ -541,9 +541,6 @@
     <t>Стоимость: 5 серебряных</t>
   </si>
   <si>
-    <t>Стоимость: 10 золотых</t>
-  </si>
-  <si>
     <t>This key must open something. Definitely.</t>
   </si>
   <si>
@@ -565,18 +562,12 @@
     <t>Этот ключ должен что-то открывать. Определенно.</t>
   </si>
   <si>
-    <t>Это зелье должно ускорять передвижение. Наверное.</t>
-  </si>
-  <si>
     <t>Монета из настоящего золота. Если верить надписи.</t>
   </si>
   <si>
     <t>The coin is made of real gold. If you believe that.</t>
   </si>
   <si>
-    <t>This potion is supposed to increase movement speed. I guess.</t>
-  </si>
-  <si>
     <t>Стоимость: 16 серебрянных</t>
   </si>
   <si>
@@ -614,6 +605,63 @@
   </si>
   <si>
     <t>SharkyNPC_2</t>
+  </si>
+  <si>
+    <t>Это зелье должно усилить прыжок. Наверное.</t>
+  </si>
+  <si>
+    <t>This potion is supposed to increase jump power. I guess.</t>
+  </si>
+  <si>
+    <t>Emerald_Header</t>
+  </si>
+  <si>
+    <t>Emerald_Cost</t>
+  </si>
+  <si>
+    <t>Emerald_Description</t>
+  </si>
+  <si>
+    <t>Emerald</t>
+  </si>
+  <si>
+    <t>Изумруд</t>
+  </si>
+  <si>
+    <t>Cost: 20 gold coins</t>
+  </si>
+  <si>
+    <t>Стоимость: 20 золотых монет</t>
+  </si>
+  <si>
+    <t>Редкий минерал, ещё и обработанный.</t>
+  </si>
+  <si>
+    <t>It's a rare mineral, and it's also processed.</t>
+  </si>
+  <si>
+    <t>UI_Continue</t>
+  </si>
+  <si>
+    <t>UI_Controls</t>
+  </si>
+  <si>
+    <t>controls</t>
+  </si>
+  <si>
+    <t>управление</t>
+  </si>
+  <si>
+    <t>continue</t>
+  </si>
+  <si>
+    <t>продолжить</t>
+  </si>
+  <si>
+    <t>Cost: 85 gold coins</t>
+  </si>
+  <si>
+    <t>Стоимость: 85 золотых монет</t>
   </si>
 </sst>
 </file>
@@ -931,13 +979,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D74"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="18.5703125" customWidth="1"/>
+    <col min="1" max="4" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -962,7 +1010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -973,7 +1021,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -984,7 +1032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -995,7 +1043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1006,7 +1054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1017,7 +1065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1028,7 +1076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1039,7 +1087,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1050,7 +1098,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1061,7 +1109,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1072,7 +1120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1083,7 +1131,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1094,7 +1142,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1105,7 +1153,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1116,7 +1164,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1127,7 +1175,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1138,7 +1186,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1149,7 +1197,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1160,7 +1208,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1171,18 +1219,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>59</v>
       </c>
       <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
         <v>111</v>
       </c>
-      <c r="D22" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1193,7 +1241,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -1201,160 +1249,160 @@
         <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="C27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>73</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" t="s">
         <v>76</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
         <v>111</v>
       </c>
-      <c r="D28" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
-      </c>
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>111</v>
-      </c>
-      <c r="D31" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="D36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>95</v>
       </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>99</v>
       </c>
-      <c r="D38" t="s">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>101</v>
       </c>
       <c r="C39" t="s">
         <v>61</v>
@@ -1363,334 +1411,389 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>102</v>
       </c>
-      <c r="C40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="C41" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>103</v>
       </c>
-      <c r="C41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="C42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>104</v>
       </c>
-      <c r="C42" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>105</v>
       </c>
-      <c r="C43" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C44" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="D44" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>106</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" t="s">
         <v>117</v>
       </c>
-      <c r="D44" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="D46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>119</v>
       </c>
-      <c r="C46" t="s">
-        <v>118</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" t="s">
+        <v>181</v>
+      </c>
+      <c r="D48" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>120</v>
-      </c>
-      <c r="C47" t="s">
-        <v>122</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C49" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" t="s">
+        <v>135</v>
+      </c>
+      <c r="D50" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D51" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" t="s">
+        <v>131</v>
+      </c>
+      <c r="D53" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" t="s">
+        <v>158</v>
+      </c>
+      <c r="D55" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" t="s">
+        <v>156</v>
+      </c>
+      <c r="D56" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>146</v>
+      </c>
+      <c r="C57" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="D57" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" t="s">
+        <v>163</v>
+      </c>
+      <c r="D60" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" t="s">
+        <v>162</v>
+      </c>
+      <c r="D63" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" t="s">
+        <v>161</v>
+      </c>
+      <c r="D64" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" t="s">
+        <v>156</v>
+      </c>
+      <c r="D65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" t="s">
+        <v>193</v>
+      </c>
+      <c r="D66" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" t="s">
         <v>121</v>
       </c>
-      <c r="C48" t="s">
-        <v>185</v>
-      </c>
-      <c r="D48" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>124</v>
-      </c>
-      <c r="C49" t="s">
-        <v>130</v>
-      </c>
-      <c r="D49" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>125</v>
-      </c>
-      <c r="C50" t="s">
-        <v>136</v>
-      </c>
-      <c r="D50" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>126</v>
-      </c>
-      <c r="C51" t="s">
-        <v>181</v>
-      </c>
-      <c r="D51" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" t="s">
-        <v>133</v>
-      </c>
-      <c r="D52" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>128</v>
-      </c>
-      <c r="C53" t="s">
-        <v>132</v>
-      </c>
-      <c r="D53" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" t="s">
-        <v>131</v>
-      </c>
-      <c r="D54" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C55" t="s">
-        <v>159</v>
-      </c>
-      <c r="D55" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>146</v>
-      </c>
-      <c r="C56" t="s">
-        <v>157</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="D68" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" t="s">
-        <v>172</v>
-      </c>
-      <c r="D57" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C58" t="s">
-        <v>160</v>
-      </c>
-      <c r="D58" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>144</v>
-      </c>
-      <c r="C59" t="s">
-        <v>158</v>
-      </c>
-      <c r="D59" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>145</v>
-      </c>
-      <c r="C60" t="s">
-        <v>164</v>
-      </c>
-      <c r="D60" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>150</v>
-      </c>
-      <c r="C61" t="s">
-        <v>161</v>
-      </c>
-      <c r="D61" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" t="s">
-        <v>163</v>
-      </c>
-      <c r="D63" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>151</v>
-      </c>
-      <c r="C64" t="s">
-        <v>162</v>
-      </c>
-      <c r="D64" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" t="s">
+        <v>154</v>
+      </c>
+      <c r="D69" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" t="s">
-        <v>157</v>
-      </c>
-      <c r="D65" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>141</v>
-      </c>
-      <c r="C66" t="s">
-        <v>182</v>
-      </c>
-      <c r="D66" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>152</v>
-      </c>
-      <c r="C67" t="s">
-        <v>156</v>
-      </c>
-      <c r="D67" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>153</v>
-      </c>
-      <c r="C68" t="s">
-        <v>122</v>
-      </c>
-      <c r="D68" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>154</v>
-      </c>
-      <c r="C69" t="s">
-        <v>155</v>
-      </c>
-      <c r="D69" t="s">
-        <v>177</v>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>194</v>
+      </c>
+      <c r="C70" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" t="s">
+        <v>199</v>
+      </c>
+      <c r="D71" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72" t="s">
+        <v>202</v>
+      </c>
+      <c r="D72" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>203</v>
+      </c>
+      <c r="C73" t="s">
+        <v>207</v>
+      </c>
+      <c r="D73" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>204</v>
+      </c>
+      <c r="C74" t="s">
+        <v>205</v>
+      </c>
+      <c r="D74" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1702,13 +1805,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568798C2-848C-4EB1-ADFF-725305B9894F}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="1" max="3" width="18.1796875" customWidth="1"/>
+    <col min="4" max="4" width="18.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1722,37 +1825,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" t="s">
         <v>187</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" t="s">
         <v>188</v>
       </c>
-      <c r="D2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" t="s">
         <v>189</v>
-      </c>
-      <c r="D3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D4" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819CFD6F-0FFB-4F50-9A1F-831ADAB87623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153EB13B-3AD3-4C9F-A584-077760007B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2205" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="2205" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LocalizationUI" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="307">
   <si>
     <t>idstring</t>
   </si>
@@ -662,6 +662,294 @@
   </si>
   <si>
     <t>Стоимость: 85 золотых монет</t>
+  </si>
+  <si>
+    <t>UI_Controls1</t>
+  </si>
+  <si>
+    <t>UI_Controls2</t>
+  </si>
+  <si>
+    <t>UI_Controls3</t>
+  </si>
+  <si>
+    <t>UI_Controls4</t>
+  </si>
+  <si>
+    <t>UI_Controls5</t>
+  </si>
+  <si>
+    <t>UI_Controls6</t>
+  </si>
+  <si>
+    <t>UI_Controls7</t>
+  </si>
+  <si>
+    <t>UI_Controls8</t>
+  </si>
+  <si>
+    <t>UI_Controls9</t>
+  </si>
+  <si>
+    <t>UI_Controls10</t>
+  </si>
+  <si>
+    <t>UI_Controls11</t>
+  </si>
+  <si>
+    <t>UI_Controls12</t>
+  </si>
+  <si>
+    <t>F5 - quick save</t>
+  </si>
+  <si>
+    <t>F9 - quick load</t>
+  </si>
+  <si>
+    <t>C - activate defense (if upgraded)</t>
+  </si>
+  <si>
+    <t>F - drag object behind you</t>
+  </si>
+  <si>
+    <t>MMB - switch quick‑slots and scroll panels</t>
+  </si>
+  <si>
+    <t>RMB - ranged attack</t>
+  </si>
+  <si>
+    <t>LMB - melee attack</t>
+  </si>
+  <si>
+    <t>1 ... 6 - switch quick‑slots</t>
+  </si>
+  <si>
+    <t>Q - use item from the quick‑slot</t>
+  </si>
+  <si>
+    <t>E - interact (with doors, chests, etc.)</t>
+  </si>
+  <si>
+    <t>Space - jump</t>
+  </si>
+  <si>
+    <t>W A S D - move</t>
+  </si>
+  <si>
+    <t>W A S D - двигаться</t>
+  </si>
+  <si>
+    <t>Space - прыжок</t>
+  </si>
+  <si>
+    <t>E - взаимодействовать (с дверьми, сундуками и т.п.)</t>
+  </si>
+  <si>
+    <t>Q - использовать предмет из ячейки быстрого доступа</t>
+  </si>
+  <si>
+    <t>1 ... 6 - смена ячеек быстрого доступа</t>
+  </si>
+  <si>
+    <t>ЛКМ - атака ближнего боя</t>
+  </si>
+  <si>
+    <t>ПКМ - атака дальнего боя</t>
+  </si>
+  <si>
+    <t>СКМ - смена ячеек быстрого доступа и прокрутка панелей</t>
+  </si>
+  <si>
+    <t>F - тащить объект за собой</t>
+  </si>
+  <si>
+    <t>C - активация защиты (если прокачена)</t>
+  </si>
+  <si>
+    <t>F5 - быстрое сохранение</t>
+  </si>
+  <si>
+    <t>F9 - быстрая загрузка</t>
+  </si>
+  <si>
+    <t>Capitan_Help1</t>
+  </si>
+  <si>
+    <t>Здесь обязательно должны быть сокровища</t>
+  </si>
+  <si>
+    <t>Ха-Ха, и я их найду!</t>
+  </si>
+  <si>
+    <t>Жаль только, что корабль разбился…</t>
+  </si>
+  <si>
+    <t>ПОДСКАЗКА: Вы всегда можете посмотреть раскладку управления в настройках игры (правый верхний угол)</t>
+  </si>
+  <si>
+    <t>There must be treasure here for sure.</t>
+  </si>
+  <si>
+    <t>Ha‑ha, and I will find them!</t>
+  </si>
+  <si>
+    <t>Too bad the ship got wrecked…</t>
+  </si>
+  <si>
+    <t>And the whole crew is God knows where… Did anyone survive besides me?</t>
+  </si>
+  <si>
+    <t>Да и весь экипаж бог знает где… Выжил ли кто-то кроме меня?</t>
+  </si>
+  <si>
+    <t>HINT: You can always check the control layout in the game settings (top‑right corner).</t>
+  </si>
+  <si>
+    <t>From the developer: Not all in‑game dialogues are translated into English.</t>
+  </si>
+  <si>
+    <t>Capitan_Help2</t>
+  </si>
+  <si>
+    <t>Capitan_Help3</t>
+  </si>
+  <si>
+    <t>Capitan_Help4</t>
+  </si>
+  <si>
+    <t>Capitan_Help5</t>
+  </si>
+  <si>
+    <t>Capitan_Help6</t>
+  </si>
+  <si>
+    <t>Capitan_Help7</t>
+  </si>
+  <si>
+    <t>Не думаю, что будет здравой идей прыгать туда просто так.</t>
+  </si>
+  <si>
+    <t>Надо что-то придумать, чтобы безопасно спуститься вниз.</t>
+  </si>
+  <si>
+    <t>ПОДСКАЗКА: Некоторые предметы можно толкать</t>
+  </si>
+  <si>
+    <t>И перетащить за собой удерживая "F"</t>
+  </si>
+  <si>
+    <t>Capitan_Warning1</t>
+  </si>
+  <si>
+    <t>Capitan_Warning2</t>
+  </si>
+  <si>
+    <t>Capitan_Warning3</t>
+  </si>
+  <si>
+    <t>Capitan_Warning4</t>
+  </si>
+  <si>
+    <t>Capitan_Warning5</t>
+  </si>
+  <si>
+    <t>Capitan_Danger1</t>
+  </si>
+  <si>
+    <t>ПОДСКАЗКА: Откройте окно персонажа на клавишу "K"</t>
+  </si>
+  <si>
+    <t>И прокачайте перк Extra Jump</t>
+  </si>
+  <si>
+    <t>Также можете использовать зеленое зелье</t>
+  </si>
+  <si>
+    <t>Оно усилит ваш прыжок, но можно и приберечь</t>
+  </si>
+  <si>
+    <t>ПОДСКАЗКА: Используйте зелье (правая кнопка мыши по зелью из инвентаря)</t>
+  </si>
+  <si>
+    <t>Лучше выпить это зелье, кто знает что дальше меня ждёт?</t>
+  </si>
+  <si>
+    <t>I don't think it's a good idea to just jump down there.</t>
+  </si>
+  <si>
+    <t>We need to figure out a way to get down safely.</t>
+  </si>
+  <si>
+    <t>HINT: Some objects can be pushed.</t>
+  </si>
+  <si>
+    <t>And dragged behind you by holding "F".</t>
+  </si>
+  <si>
+    <t>HINT: Open the character window with the "K" key.</t>
+  </si>
+  <si>
+    <t>And unlock the Extra Jump perk.</t>
+  </si>
+  <si>
+    <t>You can also use the green potion.</t>
+  </si>
+  <si>
+    <t>It boosts your jump, but you can save it for later too.</t>
+  </si>
+  <si>
+    <t>Better drink it – who knows what lies ahead?</t>
+  </si>
+  <si>
+    <t>HINT: Use the potion (right‑click on it in your inventory).</t>
+  </si>
+  <si>
+    <t>Capitan_UsePotion2</t>
+  </si>
+  <si>
+    <t>Capitan_UsePotion3</t>
+  </si>
+  <si>
+    <t>Capitan_UsePotion1</t>
+  </si>
+  <si>
+    <t>Capitan_Hint1</t>
+  </si>
+  <si>
+    <t>Capitan_Hint2</t>
+  </si>
+  <si>
+    <t>Capitan_Hint3</t>
+  </si>
+  <si>
+    <t>Capitan_Hint4</t>
+  </si>
+  <si>
+    <t>От разработчика: не все диалоги в игре переведены на английский язык.</t>
+  </si>
+  <si>
+    <t>Капитан Нос: Похоже тут тупик, но есть спуск вниз.</t>
+  </si>
+  <si>
+    <t>Капитан Нос: Ха, повезло, что эта гиганская ракушка меня не достанет</t>
+  </si>
+  <si>
+    <t>Капитан Нос: О, как нельзя кстати, зелье лечения!</t>
+  </si>
+  <si>
+    <t>Капитан Нос: Похоже карта вела на этот остров</t>
+  </si>
+  <si>
+    <t>Captain Nose: Oh, a healing potion, just what I needed!</t>
+  </si>
+  <si>
+    <t>Captain Nose: Ha, lucky that giant shell can't reach me.</t>
+  </si>
+  <si>
+    <t>Captain Nose: Looks like a dead end here, but there's a way down.</t>
+  </si>
+  <si>
+    <t>Captain Nose:Looks like the map led to this island.</t>
   </si>
 </sst>
 </file>
@@ -979,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="18.54296875" customWidth="1"/>
@@ -1796,6 +2084,138 @@
         <v>206</v>
       </c>
     </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>211</v>
+      </c>
+      <c r="C75" t="s">
+        <v>234</v>
+      </c>
+      <c r="D75" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>212</v>
+      </c>
+      <c r="C76" t="s">
+        <v>233</v>
+      </c>
+      <c r="D76" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" t="s">
+        <v>232</v>
+      </c>
+      <c r="D77" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>214</v>
+      </c>
+      <c r="C78" t="s">
+        <v>231</v>
+      </c>
+      <c r="D78" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>215</v>
+      </c>
+      <c r="C79" t="s">
+        <v>230</v>
+      </c>
+      <c r="D79" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" t="s">
+        <v>229</v>
+      </c>
+      <c r="D80" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>217</v>
+      </c>
+      <c r="C81" t="s">
+        <v>228</v>
+      </c>
+      <c r="D81" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>218</v>
+      </c>
+      <c r="C82" t="s">
+        <v>227</v>
+      </c>
+      <c r="D82" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>219</v>
+      </c>
+      <c r="C83" t="s">
+        <v>226</v>
+      </c>
+      <c r="D83" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>220</v>
+      </c>
+      <c r="C84" t="s">
+        <v>225</v>
+      </c>
+      <c r="D84" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>221</v>
+      </c>
+      <c r="C85" t="s">
+        <v>223</v>
+      </c>
+      <c r="D85" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>222</v>
+      </c>
+      <c r="C86" t="s">
+        <v>224</v>
+      </c>
+      <c r="D86" t="s">
+        <v>246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1804,11 +2224,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568798C2-848C-4EB1-ADFF-725305B9894F}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="18.1796875" customWidth="1"/>
-    <col min="4" max="4" width="18.453125" customWidth="1"/>
+    <col min="1" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="90.26953125" customWidth="1"/>
+    <col min="4" max="4" width="97.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1858,6 +2279,226 @@
         <v>189</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>270</v>
+      </c>
+      <c r="C13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D13" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" t="s">
+        <v>283</v>
+      </c>
+      <c r="D15" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" t="s">
+        <v>304</v>
+      </c>
+      <c r="D17" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>294</v>
+      </c>
+      <c r="C18" t="s">
+        <v>285</v>
+      </c>
+      <c r="D18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" t="s">
+        <v>287</v>
+      </c>
+      <c r="D20" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" t="s">
+        <v>303</v>
+      </c>
+      <c r="D22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>291</v>
+      </c>
+      <c r="C23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D23" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" t="s">
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153EB13B-3AD3-4C9F-A584-077760007B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7E6B4A-8579-498B-826F-39F372D3818F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2205" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LocalizationUI" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="334">
   <si>
     <t>idstring</t>
   </si>
@@ -950,6 +950,87 @@
   </si>
   <si>
     <t>Captain Nose:Looks like the map led to this island.</t>
+  </si>
+  <si>
+    <t>Telekinetic_Header</t>
+  </si>
+  <si>
+    <t>Telekinetic_Cost</t>
+  </si>
+  <si>
+    <t>Telekinetic_Description</t>
+  </si>
+  <si>
+    <t>JumpPower_Header</t>
+  </si>
+  <si>
+    <t>JumpPower_Cost</t>
+  </si>
+  <si>
+    <t>JumpPower_Description</t>
+  </si>
+  <si>
+    <t>MultiShot_Header</t>
+  </si>
+  <si>
+    <t>MultiShot_Cost</t>
+  </si>
+  <si>
+    <t>MultiShot_Description</t>
+  </si>
+  <si>
+    <t>Cost: 25 gold coins</t>
+  </si>
+  <si>
+    <t>Cost: 10 gold coins</t>
+  </si>
+  <si>
+    <t>Jump Power</t>
+  </si>
+  <si>
+    <t>Multi Shot</t>
+  </si>
+  <si>
+    <t>Add Multi Shot</t>
+  </si>
+  <si>
+    <t>Add Jump Power</t>
+  </si>
+  <si>
+    <t>Telekinesis</t>
+  </si>
+  <si>
+    <t>Add Telekinesis</t>
+  </si>
+  <si>
+    <t>Телекинез</t>
+  </si>
+  <si>
+    <t>Стоимость: 25 золотых монет</t>
+  </si>
+  <si>
+    <t>Добавляет телекинез, возможность перетаскивать некоторые предметы мышью.</t>
+  </si>
+  <si>
+    <t>Стоимость: 10 золотых монет</t>
+  </si>
+  <si>
+    <t>Добавляет возможность сделать тройной выстрел или бросок. Для этого надо зажать ПКМ.</t>
+  </si>
+  <si>
+    <t>Мульти выстрел</t>
+  </si>
+  <si>
+    <t>Добавляет силы вашему прыжку, сможете прыгать немного выше.</t>
+  </si>
+  <si>
+    <t>UI_ContinueDialog</t>
+  </si>
+  <si>
+    <t>Continue…</t>
+  </si>
+  <si>
+    <t>Продолжить…</t>
   </si>
 </sst>
 </file>
@@ -1267,13 +1348,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D86"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D96"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="18.54296875" customWidth="1"/>
+    <col min="1" max="4" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1287,7 +1368,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1298,7 +1379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1309,7 +1390,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1320,7 +1401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1331,7 +1412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1342,7 +1423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1353,7 +1434,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1364,7 +1445,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1375,7 +1456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1386,7 +1467,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1397,7 +1478,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1408,7 +1489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1419,7 +1500,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1430,7 +1511,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1441,7 +1522,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1452,7 +1533,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1463,7 +1544,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1474,7 +1555,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1485,7 +1566,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1496,7 +1577,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1507,7 +1588,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1518,7 +1599,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1529,7 +1610,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -1540,7 +1621,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -1551,7 +1632,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -1562,7 +1643,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -1573,7 +1654,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1584,7 +1665,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1595,7 +1676,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>79</v>
       </c>
@@ -1606,7 +1687,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>80</v>
       </c>
@@ -1617,7 +1698,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -1628,7 +1709,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>85</v>
       </c>
@@ -1639,7 +1720,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>86</v>
       </c>
@@ -1650,7 +1731,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>87</v>
       </c>
@@ -1661,7 +1742,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -1672,12 +1753,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>96</v>
       </c>
@@ -1688,7 +1769,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>100</v>
       </c>
@@ -1699,7 +1780,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>101</v>
       </c>
@@ -1710,7 +1791,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>102</v>
       </c>
@@ -1721,7 +1802,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>103</v>
       </c>
@@ -1732,7 +1813,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>104</v>
       </c>
@@ -1743,7 +1824,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>105</v>
       </c>
@@ -1754,7 +1835,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>106</v>
       </c>
@@ -1765,7 +1846,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -1776,7 +1857,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>119</v>
       </c>
@@ -1787,7 +1868,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>120</v>
       </c>
@@ -1798,7 +1879,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>123</v>
       </c>
@@ -1809,7 +1890,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>124</v>
       </c>
@@ -1820,7 +1901,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>125</v>
       </c>
@@ -1831,7 +1912,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>126</v>
       </c>
@@ -1842,7 +1923,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>127</v>
       </c>
@@ -1853,7 +1934,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>128</v>
       </c>
@@ -1864,7 +1945,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>147</v>
       </c>
@@ -1875,7 +1956,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>145</v>
       </c>
@@ -1886,7 +1967,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>146</v>
       </c>
@@ -1897,7 +1978,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>148</v>
       </c>
@@ -1908,7 +1989,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>143</v>
       </c>
@@ -1919,7 +2000,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>144</v>
       </c>
@@ -1930,7 +2011,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>149</v>
       </c>
@@ -1941,7 +2022,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>141</v>
       </c>
@@ -1952,7 +2033,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>142</v>
       </c>
@@ -1963,7 +2044,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>150</v>
       </c>
@@ -1974,7 +2055,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>139</v>
       </c>
@@ -1985,7 +2066,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>140</v>
       </c>
@@ -1996,7 +2077,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>151</v>
       </c>
@@ -2007,7 +2088,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>152</v>
       </c>
@@ -2018,7 +2099,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -2029,7 +2110,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>194</v>
       </c>
@@ -2040,7 +2121,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>195</v>
       </c>
@@ -2051,7 +2132,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>196</v>
       </c>
@@ -2062,7 +2143,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>203</v>
       </c>
@@ -2073,7 +2154,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>204</v>
       </c>
@@ -2084,7 +2165,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>211</v>
       </c>
@@ -2095,7 +2176,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>212</v>
       </c>
@@ -2106,7 +2187,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>213</v>
       </c>
@@ -2117,7 +2198,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>214</v>
       </c>
@@ -2128,7 +2209,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>215</v>
       </c>
@@ -2139,7 +2220,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>216</v>
       </c>
@@ -2150,7 +2231,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>217</v>
       </c>
@@ -2161,7 +2242,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>218</v>
       </c>
@@ -2172,7 +2253,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>219</v>
       </c>
@@ -2183,7 +2264,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>220</v>
       </c>
@@ -2194,7 +2275,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>221</v>
       </c>
@@ -2205,7 +2286,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>222</v>
       </c>
@@ -2214,6 +2295,116 @@
       </c>
       <c r="D86" t="s">
         <v>246</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>307</v>
+      </c>
+      <c r="C87" t="s">
+        <v>322</v>
+      </c>
+      <c r="D87" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>308</v>
+      </c>
+      <c r="C88" t="s">
+        <v>316</v>
+      </c>
+      <c r="D88" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>309</v>
+      </c>
+      <c r="C89" t="s">
+        <v>323</v>
+      </c>
+      <c r="D89" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>310</v>
+      </c>
+      <c r="C90" t="s">
+        <v>318</v>
+      </c>
+      <c r="D90" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>311</v>
+      </c>
+      <c r="C91" t="s">
+        <v>317</v>
+      </c>
+      <c r="D91" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>312</v>
+      </c>
+      <c r="C92" t="s">
+        <v>321</v>
+      </c>
+      <c r="D92" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" t="s">
+        <v>319</v>
+      </c>
+      <c r="D93" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>314</v>
+      </c>
+      <c r="C94" t="s">
+        <v>199</v>
+      </c>
+      <c r="D94" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>315</v>
+      </c>
+      <c r="C95" t="s">
+        <v>320</v>
+      </c>
+      <c r="D95" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>331</v>
+      </c>
+      <c r="C96" t="s">
+        <v>332</v>
+      </c>
+      <c r="D96" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -2225,14 +2416,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568798C2-848C-4EB1-ADFF-725305B9894F}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.1796875" customWidth="1"/>
-    <col min="3" max="3" width="90.26953125" customWidth="1"/>
-    <col min="4" max="4" width="97.08984375" customWidth="1"/>
+    <col min="1" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="90.28515625" customWidth="1"/>
+    <col min="4" max="4" width="97.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2246,7 +2437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>183</v>
       </c>
@@ -2257,7 +2448,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>191</v>
       </c>
@@ -2268,7 +2459,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -2279,7 +2470,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>247</v>
       </c>
@@ -2290,7 +2481,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>259</v>
       </c>
@@ -2301,7 +2492,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>260</v>
       </c>
@@ -2312,7 +2503,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -2323,7 +2514,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>262</v>
       </c>
@@ -2334,7 +2525,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>263</v>
       </c>
@@ -2345,7 +2536,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>264</v>
       </c>
@@ -2356,7 +2547,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>269</v>
       </c>
@@ -2367,7 +2558,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>270</v>
       </c>
@@ -2378,7 +2569,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>271</v>
       </c>
@@ -2389,7 +2580,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>272</v>
       </c>
@@ -2400,7 +2591,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>273</v>
       </c>
@@ -2411,7 +2602,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>274</v>
       </c>
@@ -2422,7 +2613,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>294</v>
       </c>
@@ -2433,7 +2624,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>295</v>
       </c>
@@ -2444,7 +2635,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>296</v>
       </c>
@@ -2455,7 +2646,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>297</v>
       </c>
@@ -2466,7 +2657,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>293</v>
       </c>
@@ -2477,7 +2668,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>291</v>
       </c>
@@ -2488,7 +2679,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>292</v>
       </c>

--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7E6B4A-8579-498B-826F-39F372D3818F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA3E30B-45CA-47C3-BE56-C13CF11DEB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="367">
   <si>
     <t>idstring</t>
   </si>
@@ -991,18 +991,9 @@
     <t>Multi Shot</t>
   </si>
   <si>
-    <t>Add Multi Shot</t>
-  </si>
-  <si>
-    <t>Add Jump Power</t>
-  </si>
-  <si>
     <t>Telekinesis</t>
   </si>
   <si>
-    <t>Add Telekinesis</t>
-  </si>
-  <si>
     <t>Телекинез</t>
   </si>
   <si>
@@ -1031,6 +1022,114 @@
   </si>
   <si>
     <t>Продолжить…</t>
+  </si>
+  <si>
+    <t>Ruby_Header</t>
+  </si>
+  <si>
+    <t>Ruby_Cost</t>
+  </si>
+  <si>
+    <t>Ruby_Description</t>
+  </si>
+  <si>
+    <t>Diamond_Header</t>
+  </si>
+  <si>
+    <t>Diamond_Cost</t>
+  </si>
+  <si>
+    <t>Diamond_Description</t>
+  </si>
+  <si>
+    <t>Ruby</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>Усиленный прыжок</t>
+  </si>
+  <si>
+    <t>Cost: 60 gold coins</t>
+  </si>
+  <si>
+    <t>Cost: 40 gold coins</t>
+  </si>
+  <si>
+    <t>Стоимость: 40 золотых монет</t>
+  </si>
+  <si>
+    <t>Стоимость: 60 золотых монет</t>
+  </si>
+  <si>
+    <t>Алмаз</t>
+  </si>
+  <si>
+    <t>Рубин</t>
+  </si>
+  <si>
+    <t>Captain Nose: I need a key to open this door.</t>
+  </si>
+  <si>
+    <t>Капитан Нос: Мне нужен ключ, чтобы открыть эту дверь.</t>
+  </si>
+  <si>
+    <t>NeedAKey_Door</t>
+  </si>
+  <si>
+    <t>NeedAKey_Chest</t>
+  </si>
+  <si>
+    <t>Капитан Нос: Мне нужен ключ, чтобы открыть этот сундук.</t>
+  </si>
+  <si>
+    <t>Captain Nose: I need a key to open this chest.</t>
+  </si>
+  <si>
+    <t>NoTurningBack</t>
+  </si>
+  <si>
+    <t>Captain Nose: There is no turning back!</t>
+  </si>
+  <si>
+    <t>Капитан Нос: Назад дороги нет!</t>
+  </si>
+  <si>
+    <t>Shield_Header</t>
+  </si>
+  <si>
+    <t>Shield_Cost</t>
+  </si>
+  <si>
+    <t>Shield_Description</t>
+  </si>
+  <si>
+    <t>Cost: 95 gold coins</t>
+  </si>
+  <si>
+    <t>Psionic Shield</t>
+  </si>
+  <si>
+    <t>Пси-щит</t>
+  </si>
+  <si>
+    <t>Стоимость: 95 золотых монет</t>
+  </si>
+  <si>
+    <t>Adds the ability to perform a triple shot or throw. To do this, hold down the RMB (right mouse button).</t>
+  </si>
+  <si>
+    <t>Boosts your jump power, allowing you to jump slightly higher.</t>
+  </si>
+  <si>
+    <t>Adds telekinesis, allowing you to drag certain objects with your mouse.</t>
+  </si>
+  <si>
+    <t>Grants a psionic shield that increases your defense to maximum. Duration: 3 seconds, cooldown: 15 seconds. Activation key: C</t>
+  </si>
+  <si>
+    <t>Добавляет псионический щит, который увеличивает вашу защиту до максимума. Действует 3 секунды, перезарядка 15 секунд. Активация на клавишу: C</t>
   </si>
 </sst>
 </file>
@@ -1348,10 +1447,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="64.42578125" customWidth="1"/>
+    <col min="4" max="4" width="73.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2302,10 +2403,10 @@
         <v>307</v>
       </c>
       <c r="C87" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D87" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2316,7 +2417,7 @@
         <v>316</v>
       </c>
       <c r="D88" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2324,10 +2425,10 @@
         <v>309</v>
       </c>
       <c r="C89" t="s">
+        <v>364</v>
+      </c>
+      <c r="D89" t="s">
         <v>323</v>
-      </c>
-      <c r="D89" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2338,7 +2439,7 @@
         <v>318</v>
       </c>
       <c r="D90" t="s">
-        <v>70</v>
+        <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2349,7 +2450,7 @@
         <v>317</v>
       </c>
       <c r="D91" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2357,10 +2458,10 @@
         <v>312</v>
       </c>
       <c r="C92" t="s">
-        <v>321</v>
+        <v>363</v>
       </c>
       <c r="D92" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2371,7 +2472,7 @@
         <v>319</v>
       </c>
       <c r="D93" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2390,21 +2491,120 @@
         <v>315</v>
       </c>
       <c r="C95" t="s">
-        <v>320</v>
+        <v>362</v>
       </c>
       <c r="D95" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>328</v>
+      </c>
+      <c r="C96" t="s">
+        <v>329</v>
+      </c>
+      <c r="D96" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>331</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C97" t="s">
+        <v>337</v>
+      </c>
+      <c r="D97" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>332</v>
       </c>
-      <c r="D96" t="s">
+      <c r="C98" t="s">
+        <v>341</v>
+      </c>
+      <c r="D98" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>333</v>
+      </c>
+      <c r="C99" t="s">
+        <v>202</v>
+      </c>
+      <c r="D99" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>334</v>
+      </c>
+      <c r="C100" t="s">
+        <v>338</v>
+      </c>
+      <c r="D100" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" t="s">
+        <v>340</v>
+      </c>
+      <c r="D101" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>336</v>
+      </c>
+      <c r="C102" t="s">
+        <v>202</v>
+      </c>
+      <c r="D102" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>355</v>
+      </c>
+      <c r="C103" t="s">
+        <v>359</v>
+      </c>
+      <c r="D103" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>356</v>
+      </c>
+      <c r="C104" t="s">
+        <v>358</v>
+      </c>
+      <c r="D104" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>357</v>
+      </c>
+      <c r="C105" t="s">
+        <v>365</v>
+      </c>
+      <c r="D105" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -2415,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568798C2-848C-4EB1-ADFF-725305B9894F}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.140625" customWidth="1"/>
@@ -2690,7 +2890,41 @@
         <v>279</v>
       </c>
     </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>348</v>
+      </c>
+      <c r="C25" t="s">
+        <v>346</v>
+      </c>
+      <c r="D25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" t="s">
+        <v>351</v>
+      </c>
+      <c r="D26" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>352</v>
+      </c>
+      <c r="C27" t="s">
+        <v>353</v>
+      </c>
+      <c r="D27" t="s">
+        <v>354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Exels/Localization/Localization_1.xlsx
+++ b/Assets/Exels/Localization/Localization_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\2D_platformer\Assets\Exels\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA3E30B-45CA-47C3-BE56-C13CF11DEB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53729F63-8B85-434D-93F2-C43F12182D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LocalizationUI" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="379">
   <si>
     <t>idstring</t>
   </si>
@@ -1130,6 +1130,42 @@
   </si>
   <si>
     <t>Добавляет псионический щит, который увеличивает вашу защиту до максимума. Действует 3 секунды, перезарядка 15 секунд. Активация на клавишу: C</t>
+  </si>
+  <si>
+    <t>EndGame1</t>
+  </si>
+  <si>
+    <t>EndGame2</t>
+  </si>
+  <si>
+    <t>EndGame3</t>
+  </si>
+  <si>
+    <t>EndGame4</t>
+  </si>
+  <si>
+    <t>I built this game as a portfolio project to showcase my skills as a Unity developer, focusing on implementing popular platformer mechanics,</t>
+  </si>
+  <si>
+    <t>a dialogue system, an inventory, various in‑game UI components, a localization system powered by Excel‑to‑JSON conversion, and a robust save/load system using file storage.</t>
+  </si>
+  <si>
+    <t>The code is open‑source and can be found on GitHub: https://github.com/Pirogas3/2D_platformer</t>
+  </si>
+  <si>
+    <t>Я делал её как портфолио, чтобы показать свой уровень как Unity-разработчика: здесь есть типичные механики платформеров, диалоги, инвентарь,</t>
+  </si>
+  <si>
+    <t>Исходный код открыт на GitHub: https://github.com/Pirogas3/2D_platformer</t>
+  </si>
+  <si>
+    <t>От разработчика: На данный момент игра заканчивается здесь.</t>
+  </si>
+  <si>
+    <t>From the developer: That's all for now — this is where the game currently ends.</t>
+  </si>
+  <si>
+    <t>UI-элементы, система локализации (Excel → JSON) и сохранения в файлах.</t>
   </si>
 </sst>
 </file>
@@ -1448,14 +1484,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D105"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="64.42578125" customWidth="1"/>
-    <col min="4" max="4" width="73.42578125" customWidth="1"/>
+    <col min="1" max="2" width="18.54296875" customWidth="1"/>
+    <col min="3" max="3" width="64.453125" customWidth="1"/>
+    <col min="4" max="4" width="73.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1469,7 +1505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1480,7 +1516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1491,7 +1527,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1502,7 +1538,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1513,7 +1549,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1524,7 +1560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1535,7 +1571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1546,7 +1582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1557,7 +1593,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1568,7 +1604,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1579,7 +1615,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -1590,7 +1626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -1601,7 +1637,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1612,7 +1648,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1623,7 +1659,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1634,7 +1670,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1645,7 +1681,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1656,7 +1692,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>46</v>
       </c>
@@ -1667,7 +1703,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -1678,7 +1714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1689,7 +1725,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1700,7 +1736,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1711,7 +1747,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -1722,7 +1758,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -1733,7 +1769,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -1744,7 +1780,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -1755,7 +1791,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -1766,7 +1802,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -1777,7 +1813,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>79</v>
       </c>
@@ -1788,7 +1824,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>80</v>
       </c>
@@ -1799,7 +1835,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -1810,7 +1846,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>85</v>
       </c>
@@ -1821,7 +1857,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>86</v>
       </c>
@@ -1832,7 +1868,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>87</v>
       </c>
@@ -1843,7 +1879,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>94</v>
       </c>
@@ -1854,12 +1890,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>96</v>
       </c>
@@ -1870,7 +1906,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>100</v>
       </c>
@@ -1881,7 +1917,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>101</v>
       </c>
@@ -1892,7 +1928,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>102</v>
       </c>
@@ -1903,7 +1939,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>103</v>
       </c>
@@ -1914,7 +1950,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>104</v>
       </c>
@@ -1925,7 +1961,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>105</v>
       </c>
@@ -1936,7 +1972,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>106</v>
       </c>
@@ -1947,7 +1983,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -1958,7 +1994,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>119</v>
       </c>
@@ -1969,7 +2005,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>120</v>
       </c>
@@ -1980,7 +2016,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>123</v>
       </c>
@@ -1991,7 +2027,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>124</v>
       </c>
@@ -2002,7 +2038,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>125</v>
       </c>
@@ -2013,7 +2049,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>126</v>
       </c>
@@ -2024,7 +2060,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>127</v>
       </c>
@@ -2035,7 +2071,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>128</v>
       </c>
@@ -2046,7 +2082,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>147</v>
       </c>
@@ -2057,7 +2093,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>145</v>
       </c>
@@ -2068,7 +2104,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>146</v>
       </c>
@@ -2079,7 +2115,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>148</v>
       </c>
@@ -2090,7 +2126,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>143</v>
       </c>
@@ -2101,7 +2137,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>144</v>
       </c>
@@ -2112,7 +2148,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>149</v>
       </c>
@@ -2123,7 +2159,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>141</v>
       </c>
@@ -2134,7 +2170,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>142</v>
       </c>
@@ -2145,7 +2181,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>150</v>
       </c>
@@ -2156,7 +2192,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>139</v>
       </c>
@@ -2167,7 +2203,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>140</v>
       </c>
@@ -2178,7 +2214,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>151</v>
       </c>
@@ -2189,7 +2225,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>152</v>
       </c>
@@ -2200,7 +2236,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -2211,7 +2247,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>194</v>
       </c>
@@ -2222,7 +2258,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>195</v>
       </c>
@@ -2233,7 +2269,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>196</v>
       </c>
@@ -2244,7 +2280,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>203</v>
       </c>
@@ -2255,7 +2291,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>204</v>
       </c>
@@ -2266,7 +2302,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>211</v>
       </c>
@@ -2277,7 +2313,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>212</v>
       </c>
@@ -2288,7 +2324,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>213</v>
       </c>
@@ -2299,7 +2335,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>214</v>
       </c>
@@ -2310,7 +2346,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>215</v>
       </c>
@@ -2321,7 +2357,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>216</v>
       </c>
@@ -2332,7 +2368,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>217</v>
       </c>
@@ -2343,7 +2379,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>218</v>
       </c>
@@ -2354,7 +2390,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>219</v>
       </c>
@@ -2365,7 +2401,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>220</v>
       </c>
@@ -2376,7 +2412,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>221</v>
       </c>
@@ -2387,7 +2423,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>222</v>
       </c>
@@ -2398,7 +2434,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>307</v>
       </c>
@@ -2409,7 +2445,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>308</v>
       </c>
@@ -2420,7 +2456,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>309</v>
       </c>
@@ -2431,7 +2467,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>310</v>
       </c>
@@ -2442,7 +2478,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>311</v>
       </c>
@@ -2453,7 +2489,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>312</v>
       </c>
@@ -2464,7 +2500,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>313</v>
       </c>
@@ -2475,7 +2511,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>314</v>
       </c>
@@ -2486,7 +2522,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>315</v>
       </c>
@@ -2497,7 +2533,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>328</v>
       </c>
@@ -2508,7 +2544,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>331</v>
       </c>
@@ -2519,7 +2555,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>332</v>
       </c>
@@ -2530,7 +2566,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>333</v>
       </c>
@@ -2541,7 +2577,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>334</v>
       </c>
@@ -2552,7 +2588,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>335</v>
       </c>
@@ -2563,7 +2599,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>336</v>
       </c>
@@ -2574,7 +2610,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>355</v>
       </c>
@@ -2585,7 +2621,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>356</v>
       </c>
@@ -2596,7 +2632,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>357</v>
       </c>
@@ -2615,15 +2651,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568798C2-848C-4EB1-ADFF-725305B9894F}">
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="90.28515625" customWidth="1"/>
-    <col min="4" max="4" width="97.140625" customWidth="1"/>
+    <col min="1" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="90.26953125" customWidth="1"/>
+    <col min="4" max="4" width="97.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2637,7 +2673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>183</v>
       </c>
@@ -2648,7 +2684,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>191</v>
       </c>
@@ -2659,7 +2695,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>190</v>
       </c>
@@ -2670,7 +2706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>247</v>
       </c>
@@ -2681,7 +2717,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>259</v>
       </c>
@@ -2692,7 +2728,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>260</v>
       </c>
@@ -2703,7 +2739,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -2714,7 +2750,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>262</v>
       </c>
@@ -2725,7 +2761,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>263</v>
       </c>
@@ -2736,7 +2772,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>264</v>
       </c>
@@ -2747,7 +2783,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>269</v>
       </c>
@@ -2758,7 +2794,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>270</v>
       </c>
@@ -2769,7 +2805,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>271</v>
       </c>
@@ -2780,7 +2816,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>272</v>
       </c>
@@ -2791,7 +2827,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>273</v>
       </c>
@@ -2802,7 +2838,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>274</v>
       </c>
@@ -2813,7 +2849,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>294</v>
       </c>
@@ -2824,7 +2860,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>295</v>
       </c>
@@ -2835,7 +2871,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>296</v>
       </c>
@@ -2846,7 +2882,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>297</v>
       </c>
@@ -2857,7 +2893,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>293</v>
       </c>
@@ -2868,7 +2904,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>291</v>
       </c>
@@ -2879,7 +2915,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>292</v>
       </c>
@@ -2890,7 +2926,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>348</v>
       </c>
@@ -2901,7 +2937,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>349</v>
       </c>
@@ -2912,7 +2948,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>352</v>
       </c>
@@ -2921,6 +2957,50 @@
       </c>
       <c r="D27" t="s">
         <v>354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>367</v>
+      </c>
+      <c r="C28" t="s">
+        <v>377</v>
+      </c>
+      <c r="D28" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>368</v>
+      </c>
+      <c r="C29" t="s">
+        <v>371</v>
+      </c>
+      <c r="D29" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>369</v>
+      </c>
+      <c r="C30" t="s">
+        <v>372</v>
+      </c>
+      <c r="D30" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>370</v>
+      </c>
+      <c r="C31" t="s">
+        <v>373</v>
+      </c>
+      <c r="D31" t="s">
+        <v>375</v>
       </c>
     </row>
   </sheetData>
